--- a/output/summary_tables/CME Module Summary Tables.xlsx
+++ b/output/summary_tables/CME Module Summary Tables.xlsx
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="28.5"/>
@@ -485,7 +485,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Compliance Monitoring &amp; Enforcement - evaluations of hazardous-waste handlers, the violations found, and the enforcement actions taken.</t>
+          <t>Compliance Monitoring &amp; Enforcement - evaluations of hazardous-waste handlers, the violations found, and the enforcement actions taken. Summarized from the CE_MASTER master file.</t>
         </is>
       </c>
       <c r="B1" s="7"/>
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Identifier: HANDLER_ID, one row per evaluation x violation x enforcement action.</t>
+          <t>Identifier: HANDLER_ID, one row per evaluation x violation x enforcement x SEP x citation combination.</t>
         </is>
       </c>
       <c r="B2" s="7"/>
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <v>2771749</v>
+        <v>2872361</v>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>46 other columns not summarized (identifiers, names, and descriptions / free-text fields).</t>
+          <t>9 other columns are not summarized because they hold record identifiers, personal names and staff identifiers, correspondence addresses and contact details, free-text notes, or the description text paired with a code that is summarized here. They are named below the table.</t>
         </is>
       </c>
       <c r="C5" s="7"/>
@@ -599,7 +599,7 @@
               <color rgb="FF000000"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t xml:space="preserve">EVAL_AGENCY
+            <t xml:space="preserve">HANDLER_ACTIVITY_LOCATION
 </t>
           </r>
           <r>
@@ -608,7 +608,7 @@
               <color rgb="FF666666"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t>Agency that conducted the compliance evaluation.</t>
+            <t>State or territory whose implementing agency is responsible for the site.</t>
           </r>
         </is>
       </c>
@@ -619,18 +619,18 @@
         </is>
       </c>
       <c r="C7" s="11">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>S - State</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="E7" s="12">
-        <v>91.4</v>
+        <v>6.8</v>
       </c>
       <c r="F7" s="10">
-        <v>2534516</v>
+        <v>195936</v>
       </c>
     </row>
     <row r="8">
@@ -639,14 +639,14 @@
       <c r="C8" s="11"/>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>E - EPA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="E8" s="12">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="F8" s="10">
-        <v>191552</v>
+        <v>192938</v>
       </c>
     </row>
     <row r="9">
@@ -655,14 +655,14 @@
       <c r="C9" s="11"/>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>C - EPA Contractor/Grantee</t>
+          <t>KY</t>
         </is>
       </c>
       <c r="E9" s="12">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="F9" s="10">
-        <v>23766</v>
+        <v>158097</v>
       </c>
     </row>
     <row r="10">
@@ -671,14 +671,14 @@
       <c r="C10" s="11"/>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>B - State Contractor/Grantee</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="E10" s="12">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="F10" s="10">
-        <v>13329</v>
+        <v>141391</v>
       </c>
     </row>
     <row r="11">
@@ -687,14 +687,14 @@
       <c r="C11" s="11"/>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>X - EPA-Initiated Oversight/Observation/Training Actions</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E11" s="12">
-        <v>0.3</v>
+        <v>4.3</v>
       </c>
       <c r="F11" s="10">
-        <v>7932</v>
+        <v>124884</v>
       </c>
     </row>
     <row r="12">
@@ -703,14 +703,14 @@
       <c r="C12" s="11"/>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>All Other (3)</t>
+          <t>All Other (57)</t>
         </is>
       </c>
       <c r="E12" s="12">
-        <v>0</v>
+        <v>71.7</v>
       </c>
       <c r="F12" s="10">
-        <v>654</v>
+        <v>2059115</v>
       </c>
     </row>
     <row r="13">
@@ -722,7 +722,7 @@
               <color rgb="FF000000"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t xml:space="preserve">EVAL_TYPE
+            <t xml:space="preserve">REGION
 </t>
           </r>
           <r>
@@ -731,7 +731,7 @@
               <color rgb="FF666666"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t>Type of compliance evaluation performed.</t>
+            <t>EPA region in which the site is located.</t>
           </r>
         </is>
       </c>
@@ -742,18 +742,18 @@
         </is>
       </c>
       <c r="C13" s="11">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>CEI - Compliance Evaluation Inspection</t>
+          <t>04</t>
         </is>
       </c>
       <c r="E13" s="12">
-        <v>61</v>
+        <v>27.6</v>
       </c>
       <c r="F13" s="10">
-        <v>1691591</v>
+        <v>792125</v>
       </c>
     </row>
     <row r="14">
@@ -762,14 +762,14 @@
       <c r="C14" s="11"/>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>NRR - Non-Financial Record Review</t>
+          <t>05</t>
         </is>
       </c>
       <c r="E14" s="12">
-        <v>7.8</v>
+        <v>22.7</v>
       </c>
       <c r="F14" s="10">
-        <v>216232</v>
+        <v>651419</v>
       </c>
     </row>
     <row r="15">
@@ -778,14 +778,14 @@
       <c r="C15" s="11"/>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>FCI - Focused Compliance Inspection</t>
+          <t>03</t>
         </is>
       </c>
       <c r="E15" s="12">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="F15" s="10">
-        <v>215555</v>
+        <v>246503</v>
       </c>
     </row>
     <row r="16">
@@ -794,14 +794,14 @@
       <c r="C16" s="11"/>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>SNY - Significant Non-Complier</t>
+          <t>02</t>
         </is>
       </c>
       <c r="E16" s="12">
-        <v>6.4</v>
+        <v>8.2</v>
       </c>
       <c r="F16" s="10">
-        <v>176594</v>
+        <v>234664</v>
       </c>
     </row>
     <row r="17">
@@ -810,14 +810,14 @@
       <c r="C17" s="11"/>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>CSE - Compliance Schedule Evaluation</t>
+          <t>07</t>
         </is>
       </c>
       <c r="E17" s="12">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="F17" s="10">
-        <v>154486</v>
+        <v>223928</v>
       </c>
     </row>
     <row r="18">
@@ -826,14 +826,14 @@
       <c r="C18" s="11"/>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>All Other (10)</t>
+          <t>All Other (5)</t>
         </is>
       </c>
       <c r="E18" s="12">
-        <v>11.4</v>
+        <v>25.2</v>
       </c>
       <c r="F18" s="10">
-        <v>317291</v>
+        <v>723722</v>
       </c>
     </row>
     <row r="19">
@@ -845,7 +845,7 @@
               <color rgb="FF000000"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t xml:space="preserve">FOUND_VIOLATION
+            <t xml:space="preserve">STATE
 </t>
           </r>
           <r>
@@ -854,7 +854,7 @@
               <color rgb="FF666666"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t>Whether the evaluation found a violation.</t>
+            <t>State in which the site is located.</t>
           </r>
         </is>
       </c>
@@ -865,18 +865,18 @@
         </is>
       </c>
       <c r="C19" s="11">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Y - Violation Found</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="E19" s="12">
-        <v>73.1</v>
+        <v>6.8</v>
       </c>
       <c r="F19" s="10">
-        <v>2024955</v>
+        <v>195983</v>
       </c>
     </row>
     <row r="20">
@@ -885,14 +885,14 @@
       <c r="C20" s="11"/>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>N - No Violation</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="E20" s="12">
-        <v>26.6</v>
+        <v>6.7</v>
       </c>
       <c r="F20" s="10">
-        <v>736675</v>
+        <v>192951</v>
       </c>
     </row>
     <row r="21">
@@ -901,57 +901,30 @@
       <c r="C21" s="11"/>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>U - Undetermined</t>
+          <t>KY</t>
         </is>
       </c>
       <c r="E21" s="12">
-        <v>0.4</v>
+        <v>5.5</v>
       </c>
       <c r="F21" s="10">
-        <v>10119</v>
+        <v>158098</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t xml:space="preserve">REGION
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF666666"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t>EPA region in which the site is located.</t>
-          </r>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>0%
-(0)</t>
-        </is>
-      </c>
-      <c r="C22" s="11">
-        <v>10</v>
-      </c>
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="E22" s="12">
-        <v>27.2</v>
+        <v>4.9</v>
       </c>
       <c r="F22" s="10">
-        <v>753768</v>
+        <v>141442</v>
       </c>
     </row>
     <row r="23">
@@ -960,14 +933,14 @@
       <c r="C23" s="11"/>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E23" s="12">
-        <v>22.8</v>
+        <v>4.3</v>
       </c>
       <c r="F23" s="10">
-        <v>631497</v>
+        <v>124928</v>
       </c>
     </row>
     <row r="24">
@@ -976,30 +949,57 @@
       <c r="C24" s="11"/>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>All Other (57)</t>
         </is>
       </c>
       <c r="E24" s="12">
-        <v>8.7</v>
+        <v>71.7</v>
       </c>
       <c r="F24" s="10">
-        <v>240455</v>
+        <v>2058959</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">LAND_TYPE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Ownership type of the land on which the site is located.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>6.9%
+(198310)</t>
+        </is>
+      </c>
+      <c r="C25" s="11">
+        <v>8</v>
+      </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>P - Private</t>
         </is>
       </c>
       <c r="E25" s="12">
-        <v>8.3</v>
+        <v>82.5</v>
       </c>
       <c r="F25" s="10">
-        <v>228861</v>
+        <v>2368525</v>
       </c>
     </row>
     <row r="26">
@@ -1008,14 +1008,14 @@
       <c r="C26" s="11"/>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>O - Other</t>
         </is>
       </c>
       <c r="E26" s="12">
-        <v>7.8</v>
+        <v>3.4</v>
       </c>
       <c r="F26" s="10">
-        <v>217131</v>
+        <v>97429</v>
       </c>
     </row>
     <row r="27">
@@ -1024,57 +1024,30 @@
       <c r="C27" s="11"/>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>All Other (5)</t>
+          <t>F - Federal</t>
         </is>
       </c>
       <c r="E27" s="12">
-        <v>25.3</v>
+        <v>2.8</v>
       </c>
       <c r="F27" s="10">
-        <v>700037</v>
+        <v>80264</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t xml:space="preserve">EVAL_ACTIVITY_LOCATION
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF666666"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t>State or territory whose implementing agency is responsible for the evaluation.</t>
-          </r>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>0%
-(0)</t>
-        </is>
-      </c>
-      <c r="C28" s="11">
-        <v>62</v>
-      </c>
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>S - State</t>
         </is>
       </c>
       <c r="E28" s="12">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="F28" s="10">
-        <v>186780</v>
+        <v>58521</v>
       </c>
     </row>
     <row r="29">
@@ -1083,14 +1056,14 @@
       <c r="C29" s="11"/>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>M - Municipal</t>
         </is>
       </c>
       <c r="E29" s="12">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="F29" s="10">
-        <v>174278</v>
+        <v>39397</v>
       </c>
     </row>
     <row r="30">
@@ -1099,30 +1072,57 @@
       <c r="C30" s="11"/>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>KY</t>
+          <t>All Other (3)</t>
         </is>
       </c>
       <c r="E30" s="12">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="F30" s="10">
-        <v>157608</v>
+        <v>29915</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">EVAL_ACTIVITY_LOCATION
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>State or territory whose implementing agency is responsible for the evaluation.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>0%
+(0)</t>
+        </is>
+      </c>
+      <c r="C31" s="11">
+        <v>62</v>
+      </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="E31" s="12">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="F31" s="10">
-        <v>137158</v>
+        <v>195634</v>
       </c>
     </row>
     <row r="32">
@@ -1131,14 +1131,14 @@
       <c r="C32" s="11"/>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="E32" s="12">
-        <v>4.5</v>
+        <v>6.7</v>
       </c>
       <c r="F32" s="10">
-        <v>124034</v>
+        <v>193026</v>
       </c>
     </row>
     <row r="33">
@@ -1147,57 +1147,30 @@
       <c r="C33" s="11"/>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>All Other (57)</t>
+          <t>KY</t>
         </is>
       </c>
       <c r="E33" s="12">
-        <v>71.9</v>
+        <v>5.5</v>
       </c>
       <c r="F33" s="10">
-        <v>1991891</v>
+        <v>158101</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t xml:space="preserve">LAND_TYPE
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF666666"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t>Ownership type of the land on which the site is located.</t>
-          </r>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>7%
-(194436)</t>
-        </is>
-      </c>
-      <c r="C34" s="11">
-        <v>8</v>
-      </c>
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>P - Private</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="E34" s="12">
-        <v>82.2</v>
+        <v>4.9</v>
       </c>
       <c r="F34" s="10">
-        <v>2279369</v>
+        <v>140985</v>
       </c>
     </row>
     <row r="35">
@@ -1206,14 +1179,14 @@
       <c r="C35" s="11"/>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>O - Other</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="E35" s="12">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="F35" s="10">
-        <v>96009</v>
+        <v>124650</v>
       </c>
     </row>
     <row r="36">
@@ -1222,30 +1195,57 @@
       <c r="C36" s="11"/>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>F - Federal</t>
+          <t>All Other (57)</t>
         </is>
       </c>
       <c r="E36" s="12">
-        <v>2.8</v>
+        <v>71.7</v>
       </c>
       <c r="F36" s="10">
-        <v>77799</v>
+        <v>2059965</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">EVAL_TYPE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Type of compliance evaluation performed.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>0%
+(0)</t>
+        </is>
+      </c>
+      <c r="C37" s="11">
+        <v>15</v>
+      </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>S - State</t>
+          <t>CEI - Compliance Evaluation Inspection</t>
         </is>
       </c>
       <c r="E37" s="12">
-        <v>2.1</v>
+        <v>61.1</v>
       </c>
       <c r="F37" s="10">
-        <v>56828</v>
+        <v>1754154</v>
       </c>
     </row>
     <row r="38">
@@ -1254,14 +1254,14 @@
       <c r="C38" s="11"/>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>M - Municipal</t>
+          <t>NRR - Non-Financial Record Review</t>
         </is>
       </c>
       <c r="E38" s="12">
-        <v>1.4</v>
+        <v>7.8</v>
       </c>
       <c r="F38" s="10">
-        <v>38453</v>
+        <v>222936</v>
       </c>
     </row>
     <row r="39">
@@ -1270,57 +1270,30 @@
       <c r="C39" s="11"/>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>All Other (3)</t>
+          <t>FCI - Focused Compliance Inspection</t>
         </is>
       </c>
       <c r="E39" s="12">
-        <v>1</v>
+        <v>7.6</v>
       </c>
       <c r="F39" s="10">
-        <v>28855</v>
+        <v>217451</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t xml:space="preserve">VIOL_TYPE
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF666666"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t>Regulatory area of the violation.</t>
-          </r>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>26.9%
-(746252)</t>
-        </is>
-      </c>
-      <c r="C40" s="11">
-        <v>120</v>
-      </c>
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>262.A - Generators - General</t>
+          <t>SNY - Significant Non-Complier</t>
         </is>
       </c>
       <c r="E40" s="12">
-        <v>17.7</v>
+        <v>6.7</v>
       </c>
       <c r="F40" s="10">
-        <v>491630</v>
+        <v>192995</v>
       </c>
     </row>
     <row r="41">
@@ -1329,14 +1302,14 @@
       <c r="C41" s="11"/>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>262.C - Generators - Pre-Transport</t>
+          <t>CSE - Compliance Schedule Evaluation</t>
         </is>
       </c>
       <c r="E41" s="12">
-        <v>16.2</v>
+        <v>5.4</v>
       </c>
       <c r="F41" s="10">
-        <v>450231</v>
+        <v>155311</v>
       </c>
     </row>
     <row r="42">
@@ -1345,30 +1318,57 @@
       <c r="C42" s="11"/>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>XXS - State Statute Or Regulation</t>
+          <t>All Other (10)</t>
         </is>
       </c>
       <c r="E42" s="12">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="F42" s="10">
-        <v>160552</v>
+        <v>329514</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">FOCUS_AREA
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Regulatory area the evaluation concentrated on.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>92.1%
+(2644698)</t>
+        </is>
+      </c>
+      <c r="C43" s="11">
+        <v>166</v>
+      </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>262.D - Generators - Records/Reporting</t>
+          <t>V3 - Converted From V2 Rcrainfo</t>
         </is>
       </c>
       <c r="E43" s="12">
         <v>3</v>
       </c>
       <c r="F43" s="10">
-        <v>82685</v>
+        <v>87046</v>
       </c>
     </row>
     <row r="44">
@@ -1377,14 +1377,14 @@
       <c r="C44" s="11"/>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>273.B - Universal Waste - Small Quantity Handlers</t>
+          <t>CFI - Commercial Facility Inspection</t>
         </is>
       </c>
       <c r="E44" s="12">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="F44" s="10">
-        <v>78224</v>
+        <v>15406</v>
       </c>
     </row>
     <row r="45">
@@ -1393,57 +1393,30 @@
       <c r="C45" s="11"/>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>All Other (115)</t>
+          <t>OTH - Non-Tsd Inspection That Is Not A Full Cei</t>
         </is>
       </c>
       <c r="E45" s="12">
-        <v>27.5</v>
+        <v>0.3</v>
       </c>
       <c r="F45" s="10">
-        <v>762175</v>
+        <v>7710</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t xml:space="preserve">ENF_TYPE
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF666666"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t>Type of enforcement action taken.</t>
-          </r>
-        </is>
-      </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>33.7%
-(933172)</t>
-        </is>
-      </c>
-      <c r="C46" s="11">
-        <v>161</v>
-      </c>
+      <c r="A46" s="10"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>120 - Written Informal</t>
+          <t>UWR - Universal Waste Rule Inspection</t>
         </is>
       </c>
       <c r="E46" s="12">
-        <v>30.7</v>
+        <v>0.3</v>
       </c>
       <c r="F46" s="10">
-        <v>850532</v>
+        <v>7652</v>
       </c>
     </row>
     <row r="47">
@@ -1452,14 +1425,14 @@
       <c r="C47" s="11"/>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>310 - Final 3008(A) Compliance Order</t>
+          <t>CMP - Citizen Complaint Inspection</t>
         </is>
       </c>
       <c r="E47" s="12">
-        <v>7</v>
+        <v>0.2</v>
       </c>
       <c r="F47" s="10">
-        <v>193876</v>
+        <v>7161</v>
       </c>
     </row>
     <row r="48">
@@ -1468,30 +1441,57 @@
       <c r="C48" s="11"/>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>210 - Initial 3008(A) Compliance</t>
+          <t>All Other (161)</t>
         </is>
       </c>
       <c r="E48" s="12">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="F48" s="10">
-        <v>114833</v>
+        <v>102688</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">EVAL_AGENCY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Agency that conducted the compliance evaluation.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>0%
+(0)</t>
+        </is>
+      </c>
+      <c r="C49" s="11">
+        <v>8</v>
+      </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>121 - Violation Notice (Vn)</t>
+          <t>S - State</t>
         </is>
       </c>
       <c r="E49" s="12">
-        <v>2.5</v>
+        <v>90.7</v>
       </c>
       <c r="F49" s="10">
-        <v>70095</v>
+        <v>2604447</v>
       </c>
     </row>
     <row r="50">
@@ -1500,14 +1500,14 @@
       <c r="C50" s="11"/>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>125 - Dep Warning Letter</t>
+          <t>E - EPA</t>
         </is>
       </c>
       <c r="E50" s="12">
-        <v>2.2</v>
+        <v>7.7</v>
       </c>
       <c r="F50" s="10">
-        <v>61692</v>
+        <v>221541</v>
       </c>
     </row>
     <row r="51">
@@ -1516,22 +1516,2093 @@
       <c r="C51" s="11"/>
       <c r="D51" s="10" t="inlineStr">
         <is>
+          <t>C - EPA Contractor/Grantee</t>
+        </is>
+      </c>
+      <c r="E51" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="F51" s="10">
+        <v>24438</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>B - State Contractor/Grantee</t>
+        </is>
+      </c>
+      <c r="E52" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F52" s="10">
+        <v>13349</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>X - EPA-Initiated Oversight/Observation/Training Actions</t>
+        </is>
+      </c>
+      <c r="E53" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="F53" s="10">
+        <v>7932</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>All Other (3)</t>
+        </is>
+      </c>
+      <c r="E54" s="12">
+        <v>0</v>
+      </c>
+      <c r="F54" s="10">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">EVAL_SUBORGANIZATION
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Suborganization within the evaluating agency (codes are agency-specific).</t>
+          </r>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>33.2%
+(954474)</t>
+        </is>
+      </c>
+      <c r="C55" s="11">
+        <v>460</v>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="E55" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="F55" s="10">
+        <v>137577</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E56" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="F56" s="10">
+        <v>99587</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>HW</t>
+        </is>
+      </c>
+      <c r="E57" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="F57" s="10">
+        <v>95233</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+      <c r="E58" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="F58" s="10">
+        <v>93223</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>NW</t>
+        </is>
+      </c>
+      <c r="E59" s="12">
+        <v>2.6</v>
+      </c>
+      <c r="F59" s="10">
+        <v>74449</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>All Other (455)</t>
+        </is>
+      </c>
+      <c r="E60" s="12">
+        <v>49.4</v>
+      </c>
+      <c r="F60" s="10">
+        <v>1417818</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">REQUEST_AGENCY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Agency that issued the information request.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>99.8%
+(2866566)</t>
+        </is>
+      </c>
+      <c r="C61" s="11">
+        <v>3</v>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>E - EPA</t>
+        </is>
+      </c>
+      <c r="E61" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="F61" s="10">
+        <v>5353</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>S - State</t>
+        </is>
+      </c>
+      <c r="E62" s="12">
+        <v>0</v>
+      </c>
+      <c r="F62" s="10">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>C - EPA Contractor/Grantee</t>
+        </is>
+      </c>
+      <c r="E63" s="12">
+        <v>0</v>
+      </c>
+      <c r="F63" s="10">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">REQUEST_ACTIVITY_LOCATION
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>State or territory whose implementing agency is responsible for the information request.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>99.8%
+(2866566)</t>
+        </is>
+      </c>
+      <c r="C64" s="11">
+        <v>36</v>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="E64" s="12">
+        <v>0</v>
+      </c>
+      <c r="F64" s="10">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="E65" s="12">
+        <v>0</v>
+      </c>
+      <c r="F65" s="10">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="E66" s="12">
+        <v>0</v>
+      </c>
+      <c r="F66" s="10">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="E67" s="12">
+        <v>0</v>
+      </c>
+      <c r="F67" s="10">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="E68" s="12">
+        <v>0</v>
+      </c>
+      <c r="F68" s="10">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>All Other (31)</t>
+        </is>
+      </c>
+      <c r="E69" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="F69" s="10">
+        <v>2581</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">VIOL_ACTIVITY_LOCATION
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>State or territory whose implementing agency is responsible for the violation.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>26%
+(746252)</t>
+        </is>
+      </c>
+      <c r="C70" s="11">
+        <v>61</v>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="E70" s="12">
+        <v>6</v>
+      </c>
+      <c r="F70" s="10">
+        <v>172778</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="E71" s="12">
+        <v>5</v>
+      </c>
+      <c r="F71" s="10">
+        <v>144371</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="E72" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="F72" s="10">
+        <v>123010</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E73" s="12">
+        <v>4.1</v>
+      </c>
+      <c r="F73" s="10">
+        <v>117205</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E74" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="F74" s="10">
+        <v>110614</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>All Other (56)</t>
+        </is>
+      </c>
+      <c r="E75" s="12">
+        <v>50.8</v>
+      </c>
+      <c r="F75" s="10">
+        <v>1458131</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">VIOL_TYPE_OWNER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Organization that defines the violation-type code list.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>66.5%
+(1911483)</t>
+        </is>
+      </c>
+      <c r="C76" s="11">
+        <v>1</v>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>HQ - Nationally Defined Values</t>
+        </is>
+      </c>
+      <c r="E76" s="12">
+        <v>33.5</v>
+      </c>
+      <c r="F76" s="10">
+        <v>960878</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">VIOL_TYPE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Regulatory area of the violation.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>26%
+(746252)</t>
+        </is>
+      </c>
+      <c r="C77" s="11">
+        <v>120</v>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>262.A - Generators - General</t>
+        </is>
+      </c>
+      <c r="E77" s="12">
+        <v>17.5</v>
+      </c>
+      <c r="F77" s="10">
+        <v>504008</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>262.C - Generators - Pre-Transport</t>
+        </is>
+      </c>
+      <c r="E78" s="12">
+        <v>16.4</v>
+      </c>
+      <c r="F78" s="10">
+        <v>470764</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>XXS - State Statute Or Regulation</t>
+        </is>
+      </c>
+      <c r="E79" s="12">
+        <v>5.8</v>
+      </c>
+      <c r="F79" s="10">
+        <v>166001</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>262.D - Generators - Records/Reporting</t>
+        </is>
+      </c>
+      <c r="E80" s="12">
+        <v>3</v>
+      </c>
+      <c r="F80" s="10">
+        <v>86706</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>273.B - Universal Waste - Small Quantity Handlers</t>
+        </is>
+      </c>
+      <c r="E81" s="12">
+        <v>2.9</v>
+      </c>
+      <c r="F81" s="10">
+        <v>83673</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>All Other (115)</t>
+        </is>
+      </c>
+      <c r="E82" s="12">
+        <v>28.4</v>
+      </c>
+      <c r="F82" s="10">
+        <v>814957</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">VIOL_DETERMINED_BY_AGENCY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Agency that determined the violation.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>26%
+(746252)</t>
+        </is>
+      </c>
+      <c r="C83" s="11">
+        <v>2</v>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>S - State</t>
+        </is>
+      </c>
+      <c r="E83" s="12">
+        <v>67.1</v>
+      </c>
+      <c r="F83" s="10">
+        <v>1926308</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="11"/>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>E - EPA</t>
+        </is>
+      </c>
+      <c r="E84" s="12">
+        <v>7</v>
+      </c>
+      <c r="F84" s="10">
+        <v>199801</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">RESPONSIBLE_AGENCY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Agency responsible for bringing the site back into compliance.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>26.1%
+(749544)</t>
+        </is>
+      </c>
+      <c r="C85" s="11">
+        <v>5</v>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>S - State</t>
+        </is>
+      </c>
+      <c r="E85" s="12">
+        <v>66.4</v>
+      </c>
+      <c r="F85" s="10">
+        <v>1907245</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10"/>
+      <c r="B86" s="11"/>
+      <c r="C86" s="11"/>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>E - EPA</t>
+        </is>
+      </c>
+      <c r="E86" s="12">
+        <v>7.5</v>
+      </c>
+      <c r="F86" s="10">
+        <v>215550</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="11"/>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>C - EPA Contractor/Grantee</t>
+        </is>
+      </c>
+      <c r="E87" s="12">
+        <v>0</v>
+      </c>
+      <c r="F87" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="11"/>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>B - State Contractor/Grantee</t>
+        </is>
+      </c>
+      <c r="E88" s="12">
+        <v>0</v>
+      </c>
+      <c r="F88" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10"/>
+      <c r="B89" s="11"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E89" s="12">
+        <v>0</v>
+      </c>
+      <c r="F89" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">RTC_QUALIFIER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Qualifier on how the violation was returned to compliance.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>28.1%
+(807277)</t>
+        </is>
+      </c>
+      <c r="C90" s="11">
+        <v>4</v>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E90" s="12">
+        <v>33.8</v>
+      </c>
+      <c r="F90" s="10">
+        <v>972213</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10"/>
+      <c r="B91" s="11"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E91" s="12">
+        <v>29.6</v>
+      </c>
+      <c r="F91" s="10">
+        <v>849389</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10"/>
+      <c r="B92" s="11"/>
+      <c r="C92" s="11"/>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E92" s="12">
+        <v>6.6</v>
+      </c>
+      <c r="F92" s="10">
+        <v>188758</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10"/>
+      <c r="B93" s="11"/>
+      <c r="C93" s="11"/>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E93" s="12">
+        <v>1.9</v>
+      </c>
+      <c r="F93" s="10">
+        <v>54724</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">CITATION_OWNER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Organization that defines the citation code list.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>66.5%
+(1911483)</t>
+        </is>
+      </c>
+      <c r="C94" s="11">
+        <v>47</v>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>HQ - Nationally Defined Values</t>
+        </is>
+      </c>
+      <c r="E94" s="12">
+        <v>17.5</v>
+      </c>
+      <c r="F94" s="10">
+        <v>502242</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10"/>
+      <c r="B95" s="11"/>
+      <c r="C95" s="11"/>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="E95" s="12">
+        <v>2.7</v>
+      </c>
+      <c r="F95" s="10">
+        <v>76653</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10"/>
+      <c r="B96" s="11"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E96" s="12">
+        <v>2.1</v>
+      </c>
+      <c r="F96" s="10">
+        <v>61141</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10"/>
+      <c r="B97" s="11"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="E97" s="12">
+        <v>1.7</v>
+      </c>
+      <c r="F97" s="10">
+        <v>49478</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10"/>
+      <c r="B98" s="11"/>
+      <c r="C98" s="11"/>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="E98" s="12">
+        <v>1.3</v>
+      </c>
+      <c r="F98" s="10">
+        <v>37226</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10"/>
+      <c r="B99" s="11"/>
+      <c r="C99" s="11"/>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>All Other (42)</t>
+        </is>
+      </c>
+      <c r="E99" s="12">
+        <v>8.2</v>
+      </c>
+      <c r="F99" s="10">
+        <v>234138</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">CITATION
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Regulation, statute, or permit condition the violation was written under.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>66.5%
+(1911483)</t>
+        </is>
+      </c>
+      <c r="C100" s="11">
+        <v>12038</v>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>262.11</t>
+        </is>
+      </c>
+      <c r="E100" s="12">
+        <v>1.3</v>
+      </c>
+      <c r="F100" s="10">
+        <v>36395</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10"/>
+      <c r="B101" s="11"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>279.22(c)(1)</t>
+        </is>
+      </c>
+      <c r="E101" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F101" s="10">
+        <v>15013</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10"/>
+      <c r="B102" s="11"/>
+      <c r="C102" s="11"/>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>262.34(a)(2)</t>
+        </is>
+      </c>
+      <c r="E102" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F102" s="10">
+        <v>14755</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10"/>
+      <c r="B103" s="11"/>
+      <c r="C103" s="11"/>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>262.34(a)(3)</t>
+        </is>
+      </c>
+      <c r="E103" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F103" s="10">
+        <v>13409</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10"/>
+      <c r="B104" s="11"/>
+      <c r="C104" s="11"/>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>265.173(a)</t>
+        </is>
+      </c>
+      <c r="E104" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="F104" s="10">
+        <v>12838</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10"/>
+      <c r="B105" s="11"/>
+      <c r="C105" s="11"/>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>All Other (12033)</t>
+        </is>
+      </c>
+      <c r="E105" s="12">
+        <v>30.2</v>
+      </c>
+      <c r="F105" s="10">
+        <v>868468</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">CITATION_TYPE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Whether the citation is federal, state, or permit-based.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>66.5%
+(1911483)</t>
+        </is>
+      </c>
+      <c r="C106" s="11">
+        <v>6</v>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>FR - Federal Regulation</t>
+        </is>
+      </c>
+      <c r="E106" s="12">
+        <v>16.9</v>
+      </c>
+      <c r="F106" s="10">
+        <v>486751</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10"/>
+      <c r="B107" s="11"/>
+      <c r="C107" s="11"/>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>SR - State Regulation</t>
+        </is>
+      </c>
+      <c r="E107" s="12">
+        <v>14.8</v>
+      </c>
+      <c r="F107" s="10">
+        <v>425315</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10"/>
+      <c r="B108" s="11"/>
+      <c r="C108" s="11"/>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>SS - State Statute</t>
+        </is>
+      </c>
+      <c r="E108" s="12">
+        <v>1.1</v>
+      </c>
+      <c r="F108" s="10">
+        <v>32311</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10"/>
+      <c r="B109" s="11"/>
+      <c r="C109" s="11"/>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>PC - Permit Condition</t>
+        </is>
+      </c>
+      <c r="E109" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F109" s="10">
+        <v>13719</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10"/>
+      <c r="B110" s="11"/>
+      <c r="C110" s="11"/>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>FS - Federal Statute</t>
+        </is>
+      </c>
+      <c r="E110" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="F110" s="10">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10"/>
+      <c r="B111" s="11"/>
+      <c r="C111" s="11"/>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>OC - Order Condition</t>
+        </is>
+      </c>
+      <c r="E111" s="12">
+        <v>0</v>
+      </c>
+      <c r="F111" s="10">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">ENF_ACTIVITY_LOCATION
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>State or territory whose implementing agency is responsible for the enforcement action.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>32.9%
+(944345)</t>
+        </is>
+      </c>
+      <c r="C112" s="11">
+        <v>61</v>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="E112" s="12">
+        <v>5.9</v>
+      </c>
+      <c r="F112" s="10">
+        <v>168305</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10"/>
+      <c r="B113" s="11"/>
+      <c r="C113" s="11"/>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="E113" s="12">
+        <v>4.1</v>
+      </c>
+      <c r="F113" s="10">
+        <v>117727</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10"/>
+      <c r="B114" s="11"/>
+      <c r="C114" s="11"/>
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="E114" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="F114" s="10">
+        <v>107450</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10"/>
+      <c r="B115" s="11"/>
+      <c r="C115" s="11"/>
+      <c r="D115" s="10" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E115" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="F115" s="10">
+        <v>106575</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10"/>
+      <c r="B116" s="11"/>
+      <c r="C116" s="11"/>
+      <c r="D116" s="10" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E116" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="F116" s="10">
+        <v>101708</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10"/>
+      <c r="B117" s="11"/>
+      <c r="C117" s="11"/>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>All Other (56)</t>
+        </is>
+      </c>
+      <c r="E117" s="12">
+        <v>46.2</v>
+      </c>
+      <c r="F117" s="10">
+        <v>1326251</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">ENF_TYPE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Type of enforcement action taken.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>32.9%
+(944345)</t>
+        </is>
+      </c>
+      <c r="C118" s="11">
+        <v>161</v>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>120 - Written Informal</t>
+        </is>
+      </c>
+      <c r="E118" s="12">
+        <v>30.6</v>
+      </c>
+      <c r="F118" s="10">
+        <v>879057</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10"/>
+      <c r="B119" s="11"/>
+      <c r="C119" s="11"/>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>310 - Final 3008(A) Compliance Order</t>
+        </is>
+      </c>
+      <c r="E119" s="12">
+        <v>7.2</v>
+      </c>
+      <c r="F119" s="10">
+        <v>205648</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="10"/>
+      <c r="B120" s="11"/>
+      <c r="C120" s="11"/>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>210 - Initial 3008(A) Compliance</t>
+        </is>
+      </c>
+      <c r="E120" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="F120" s="10">
+        <v>122172</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10"/>
+      <c r="B121" s="11"/>
+      <c r="C121" s="11"/>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>121 - Violation Notice (Vn)</t>
+        </is>
+      </c>
+      <c r="E121" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="F121" s="10">
+        <v>70893</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="10"/>
+      <c r="B122" s="11"/>
+      <c r="C122" s="11"/>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>125 - Dep Warning Letter</t>
+        </is>
+      </c>
+      <c r="E122" s="12">
+        <v>2.3</v>
+      </c>
+      <c r="F122" s="10">
+        <v>65528</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10"/>
+      <c r="B123" s="11"/>
+      <c r="C123" s="11"/>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
           <t>All Other (156)</t>
         </is>
       </c>
-      <c r="E51" s="12">
-        <v>19.8</v>
-      </c>
-      <c r="F51" s="10">
-        <v>547549</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="14" t="inlineStr">
+      <c r="E123" s="12">
+        <v>20.4</v>
+      </c>
+      <c r="F123" s="10">
+        <v>584718</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">ENF_AGENCY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Agency that took the enforcement action.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>32.9%
+(944345)</t>
+        </is>
+      </c>
+      <c r="C124" s="11">
+        <v>2</v>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>S - State</t>
+        </is>
+      </c>
+      <c r="E124" s="12">
+        <v>61.1</v>
+      </c>
+      <c r="F124" s="10">
+        <v>1753917</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10"/>
+      <c r="B125" s="11"/>
+      <c r="C125" s="11"/>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>E - EPA</t>
+        </is>
+      </c>
+      <c r="E125" s="12">
+        <v>6.1</v>
+      </c>
+      <c r="F125" s="10">
+        <v>174099</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">ENF_SUBORGANIZATION
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Suborganization within the enforcing agency (codes are agency-specific).</t>
+          </r>
+        </is>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>53.6%
+(1539866)</t>
+        </is>
+      </c>
+      <c r="C126" s="11">
+        <v>337</v>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="E126" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="F126" s="10">
+        <v>97933</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10"/>
+      <c r="B127" s="11"/>
+      <c r="C127" s="11"/>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t>ENF</t>
+        </is>
+      </c>
+      <c r="E127" s="12">
+        <v>2.7</v>
+      </c>
+      <c r="F127" s="10">
+        <v>76313</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10"/>
+      <c r="B128" s="11"/>
+      <c r="C128" s="11"/>
+      <c r="D128" s="10" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+      <c r="E128" s="12">
+        <v>2.4</v>
+      </c>
+      <c r="F128" s="10">
+        <v>67743</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10"/>
+      <c r="B129" s="11"/>
+      <c r="C129" s="11"/>
+      <c r="D129" s="10" t="inlineStr">
+        <is>
+          <t>HW</t>
+        </is>
+      </c>
+      <c r="E129" s="12">
+        <v>2.2</v>
+      </c>
+      <c r="F129" s="10">
+        <v>64022</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="10"/>
+      <c r="B130" s="11"/>
+      <c r="C130" s="11"/>
+      <c r="D130" s="10" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E130" s="12">
+        <v>2.2</v>
+      </c>
+      <c r="F130" s="10">
+        <v>63831</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10"/>
+      <c r="B131" s="11"/>
+      <c r="C131" s="11"/>
+      <c r="D131" s="10" t="inlineStr">
+        <is>
+          <t>All Other (332)</t>
+        </is>
+      </c>
+      <c r="E131" s="12">
+        <v>33.5</v>
+      </c>
+      <c r="F131" s="10">
+        <v>962653</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">DISPOSITION_STATUS
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Where the enforcement action stands.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>95.1%
+(2731035)</t>
+        </is>
+      </c>
+      <c r="C132" s="11">
+        <v>9</v>
+      </c>
+      <c r="D132" s="10" t="inlineStr">
+        <is>
+          <t>AS - Action Satisfied (Case Closed)</t>
+        </is>
+      </c>
+      <c r="E132" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="F132" s="10">
+        <v>131818</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="10"/>
+      <c r="B133" s="11"/>
+      <c r="C133" s="11"/>
+      <c r="D133" s="10" t="inlineStr">
+        <is>
+          <t>DR - Dropped</t>
+        </is>
+      </c>
+      <c r="E133" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="F133" s="10">
+        <v>5461</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="10"/>
+      <c r="B134" s="11"/>
+      <c r="C134" s="11"/>
+      <c r="D134" s="10" t="inlineStr">
+        <is>
+          <t>PR - Open For Public Review</t>
+        </is>
+      </c>
+      <c r="E134" s="12">
+        <v>0</v>
+      </c>
+      <c r="F134" s="10">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="10"/>
+      <c r="B135" s="11"/>
+      <c r="C135" s="11"/>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>WD - Withdrawn</t>
+        </is>
+      </c>
+      <c r="E135" s="12">
+        <v>0</v>
+      </c>
+      <c r="F135" s="10">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="10"/>
+      <c r="B136" s="11"/>
+      <c r="C136" s="11"/>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>PC - Public Review Completed</t>
+        </is>
+      </c>
+      <c r="E136" s="12">
+        <v>0</v>
+      </c>
+      <c r="F136" s="10">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10"/>
+      <c r="B137" s="11"/>
+      <c r="C137" s="11"/>
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t>All Other (4)</t>
+        </is>
+      </c>
+      <c r="E137" s="12">
+        <v>0</v>
+      </c>
+      <c r="F137" s="10">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">LEAD_AGENCY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Agency leading a case handled jointly.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>99.7%
+(2863175)</t>
+        </is>
+      </c>
+      <c r="C138" s="11">
+        <v>5</v>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E138" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="F138" s="10">
+        <v>8878</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10"/>
+      <c r="B139" s="11"/>
+      <c r="C139" s="11"/>
+      <c r="D139" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E139" s="12">
+        <v>0</v>
+      </c>
+      <c r="F139" s="10">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="10"/>
+      <c r="B140" s="11"/>
+      <c r="C140" s="11"/>
+      <c r="D140" s="10" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E140" s="12">
+        <v>0</v>
+      </c>
+      <c r="F140" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10"/>
+      <c r="B141" s="11"/>
+      <c r="C141" s="11"/>
+      <c r="D141" s="10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E141" s="12">
+        <v>0</v>
+      </c>
+      <c r="F141" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="10"/>
+      <c r="B142" s="11"/>
+      <c r="C142" s="11"/>
+      <c r="D142" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E142" s="12">
+        <v>0</v>
+      </c>
+      <c r="F142" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">SEP_TYPE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Type of supplemental environmental project accepted in settlement.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B143" s="11" t="inlineStr">
+        <is>
+          <t>98.8%
+(2839258)</t>
+        </is>
+      </c>
+      <c r="C143" s="11">
+        <v>15</v>
+      </c>
+      <c r="D143" s="10" t="inlineStr">
+        <is>
+          <t>PPR - Pollution Prevention And Reduction</t>
+        </is>
+      </c>
+      <c r="E143" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="F143" s="10">
+        <v>16254</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="10"/>
+      <c r="B144" s="11"/>
+      <c r="C144" s="11"/>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>EAA - Environmental Audits And Assessment</t>
+        </is>
+      </c>
+      <c r="E144" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="F144" s="10">
+        <v>4832</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="10"/>
+      <c r="B145" s="11"/>
+      <c r="C145" s="11"/>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>EAP - Environmental Awareness Programs</t>
+        </is>
+      </c>
+      <c r="E145" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="F145" s="10">
+        <v>3930</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="10"/>
+      <c r="B146" s="11"/>
+      <c r="C146" s="11"/>
+      <c r="D146" s="10" t="inlineStr">
+        <is>
+          <t>ERE - Environmental Restoration</t>
+        </is>
+      </c>
+      <c r="E146" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="F146" s="10">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="10"/>
+      <c r="B147" s="11"/>
+      <c r="C147" s="11"/>
+      <c r="D147" s="10" t="inlineStr">
+        <is>
+          <t>EPP - Emergency Planning And Preparedness</t>
+        </is>
+      </c>
+      <c r="E147" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="F147" s="10">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="10"/>
+      <c r="B148" s="11"/>
+      <c r="C148" s="11"/>
+      <c r="D148" s="10" t="inlineStr">
+        <is>
+          <t>All Other (10)</t>
+        </is>
+      </c>
+      <c r="E148" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="F148" s="10">
+        <v>3232</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="14" t="inlineStr">
         <is>
           <t>Notes on missing values:
+FOCUS_AREA: Not applicable. Only the evaluations that targeted one regulatory area carry a focus.
+REQUEST_AGENCY / REQUEST_ACTIVITY_LOCATION: Not applicable. Few evaluations involve a formal information request.
 VIOL_TYPE: Not applicable. No violation was found.
+RTC_QUALIFIER: Not applicable. Set only once a violation has been returned to compliance.
+CITATION / CITATION_TYPE / CITATION_OWNER: Not applicable. Only violations written to a specific citation carry these.
 ENF_TYPE: Not applicable. No enforcement action followed.
+DISPOSITION_STATUS / LEAD_AGENCY: Not applicable. Recorded on the formal actions that reach a disposition.
+SEP_TYPE: Not applicable. Very few settlements include a supplemental environmental project.
 Note: EPA Regions
 EPA Region 1: Connecticut, Maine, Massachusetts, New Hampshire, Rhode Island, Vermont
 EPA Region 2: New Jersey, New York, Puerto Rico, Virgin Islands
@@ -1545,185 +3616,125 @@
 EPA Region 10: Alaska, Idaho, Oregon, Washington</t>
         </is>
       </c>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="14"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="14"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="14"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="14" t="inlineStr">
+      <c r="B150" s="14"/>
+      <c r="C150" s="14"/>
+      <c r="D150" s="14"/>
+      <c r="E150" s="14"/>
+      <c r="F150" s="14"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="14"/>
+      <c r="B151" s="14"/>
+      <c r="C151" s="14"/>
+      <c r="D151" s="14"/>
+      <c r="E151" s="14"/>
+      <c r="F151" s="14"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="14"/>
+      <c r="B152" s="14"/>
+      <c r="C152" s="14"/>
+      <c r="D152" s="14"/>
+      <c r="E152" s="14"/>
+      <c r="F152" s="14"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="14"/>
+      <c r="B153" s="14"/>
+      <c r="C153" s="14"/>
+      <c r="D153" s="14"/>
+      <c r="E153" s="14"/>
+      <c r="F153" s="14"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="14"/>
+      <c r="B154" s="14"/>
+      <c r="C154" s="14"/>
+      <c r="D154" s="14"/>
+      <c r="E154" s="14"/>
+      <c r="F154" s="14"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="14"/>
+      <c r="B155" s="14"/>
+      <c r="C155" s="14"/>
+      <c r="D155" s="14"/>
+      <c r="E155" s="14"/>
+      <c r="F155" s="14"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="14"/>
+      <c r="B156" s="14"/>
+      <c r="C156" s="14"/>
+      <c r="D156" s="14"/>
+      <c r="E156" s="14"/>
+      <c r="F156" s="14"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="14"/>
+      <c r="B157" s="14"/>
+      <c r="C157" s="14"/>
+      <c r="D157" s="14"/>
+      <c r="E157" s="14"/>
+      <c r="F157" s="14"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="14"/>
+      <c r="B158" s="14"/>
+      <c r="C158" s="14"/>
+      <c r="D158" s="14"/>
+      <c r="E158" s="14"/>
+      <c r="F158" s="14"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="14"/>
+      <c r="B159" s="14"/>
+      <c r="C159" s="14"/>
+      <c r="D159" s="14"/>
+      <c r="E159" s="14"/>
+      <c r="F159" s="14"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="14" t="inlineStr">
         <is>
           <t>Variables dropped (present in the source file but not summarized):
-'EVAL_IDENTIFIER', 'FOCUS_AREA', 'FOCUS_AREA_DESC',
-'EVAL_RESPONSIBLE_PERSON', 'EVAL_SUBORGANIZATION',
-'HANDLER_ACTIVITY_LOCATION', 'HANDLER_NAME', 'STATE', 'REQUEST_SEQ',
-'DATE_OF_REQUEST', 'DATE_RESPONSE_RECEIVED', 'REQUEST_AGENCY',
-'REQUEST_ACTIVITY_LOCATION', 'VIOL_ACTIVITY_LOCATION', 'VIOL_SEQ',
-'VIOL_DETERMINED_BY_AGENCY', 'FORMER_CITATION', 'RTC_QUALIFIER',
-'RESPONSIBLE_AGENCY', 'SCHEDULED_COMPLIANCE_DATE', 'ENF_ACTIVITY_LOCATION',
-'ENF_IDENTIFIER', 'ENF_AGENCY', 'DOCKET_NUMBER', 'ATTORNEY',
-'APPEAL_INITIATED_DATE', 'APPEAL_RESOLVED_DATE', 'DISPOSITION_STATUS_DATE',
-'DISPOSITION_STATUS', 'DISPOSITION_STATUS_DESC', 'CAFO_SEQ',
-'RESPONDENT_NAME', 'LEAD_AGENCY', 'ENF_RESPONSIBLE_PERSON',
-'ENF_SUBORGANIZATION', 'SEP_SEQ', 'EXPENDITURE_AMOUNT',
-'SCHEDULED_COMPLETION_DATE', 'ACTUAL_COMPLETION_DATE', 'SEP_DEFAULTED_DATE',
-'SEP_TYPE', 'SEP_TYPE_DESC', 'FINAL_COUNT', 'VIOL_LAST_CHANGE',
-'ENF_LAST_CHANGE', 'NOC_DATE'</t>
-        </is>
-      </c>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="14"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="14"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="14"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="14"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="14"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="14"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="14"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="14"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="14"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="14"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="14"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="14"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="14"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="14"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="14"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
+'EVAL_IDENTIFIER', 'ENF_IDENTIFIER', 'HANDLER_NAME',
+'EVAL_RESPONSIBLE_PERSON', 'FORMER_CITATION', 'DOCKET_NUMBER', 'ATTORNEY',
+'ENF_RESPONSIBLE_PERSON', 'RESPONDENT_NAME'</t>
+        </is>
+      </c>
+      <c r="B161" s="14"/>
+      <c r="C161" s="14"/>
+      <c r="D161" s="14"/>
+      <c r="E161" s="14"/>
+      <c r="F161" s="14"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="14"/>
+      <c r="B162" s="14"/>
+      <c r="C162" s="14"/>
+      <c r="D162" s="14"/>
+      <c r="E162" s="14"/>
+      <c r="F162" s="14"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="14"/>
+      <c r="B163" s="14"/>
+      <c r="C163" s="14"/>
+      <c r="D163" s="14"/>
+      <c r="E163" s="14"/>
+      <c r="F163" s="14"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="14"/>
+      <c r="B164" s="14"/>
+      <c r="C164" s="14"/>
+      <c r="D164" s="14"/>
+      <c r="E164" s="14"/>
+      <c r="F164" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="85">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C3:C4"/>
@@ -1735,26 +3746,80 @@
     <mergeCell ref="A13:A18"/>
     <mergeCell ref="B13:B18"/>
     <mergeCell ref="C13:C18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="A22:A27"/>
-    <mergeCell ref="B22:B27"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="B28:B33"/>
-    <mergeCell ref="C28:C33"/>
-    <mergeCell ref="A34:A39"/>
-    <mergeCell ref="B34:B39"/>
-    <mergeCell ref="C34:C39"/>
-    <mergeCell ref="A40:A45"/>
-    <mergeCell ref="B40:B45"/>
-    <mergeCell ref="C40:C45"/>
-    <mergeCell ref="A46:A51"/>
-    <mergeCell ref="B46:B51"/>
-    <mergeCell ref="C46:C51"/>
-    <mergeCell ref="A53:F56"/>
-    <mergeCell ref="A58:F73"/>
+    <mergeCell ref="A19:A24"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="A25:A30"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="A31:A36"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="C31:C36"/>
+    <mergeCell ref="A37:A42"/>
+    <mergeCell ref="B37:B42"/>
+    <mergeCell ref="C37:C42"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="B43:B48"/>
+    <mergeCell ref="C43:C48"/>
+    <mergeCell ref="A49:A54"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="C49:C54"/>
+    <mergeCell ref="A55:A60"/>
+    <mergeCell ref="B55:B60"/>
+    <mergeCell ref="C55:C60"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="C61:C63"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="B64:B69"/>
+    <mergeCell ref="C64:C69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="B70:B75"/>
+    <mergeCell ref="C70:C75"/>
+    <mergeCell ref="A77:A82"/>
+    <mergeCell ref="B77:B82"/>
+    <mergeCell ref="C77:C82"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="A85:A89"/>
+    <mergeCell ref="B85:B89"/>
+    <mergeCell ref="C85:C89"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="A94:A99"/>
+    <mergeCell ref="B94:B99"/>
+    <mergeCell ref="C94:C99"/>
+    <mergeCell ref="A100:A105"/>
+    <mergeCell ref="B100:B105"/>
+    <mergeCell ref="C100:C105"/>
+    <mergeCell ref="A106:A111"/>
+    <mergeCell ref="B106:B111"/>
+    <mergeCell ref="C106:C111"/>
+    <mergeCell ref="A112:A117"/>
+    <mergeCell ref="B112:B117"/>
+    <mergeCell ref="C112:C117"/>
+    <mergeCell ref="A118:A123"/>
+    <mergeCell ref="B118:B123"/>
+    <mergeCell ref="C118:C123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="C124:C125"/>
+    <mergeCell ref="A126:A131"/>
+    <mergeCell ref="B126:B131"/>
+    <mergeCell ref="C126:C131"/>
+    <mergeCell ref="A132:A137"/>
+    <mergeCell ref="B132:B137"/>
+    <mergeCell ref="C132:C137"/>
+    <mergeCell ref="A138:A142"/>
+    <mergeCell ref="B138:B142"/>
+    <mergeCell ref="C138:C142"/>
+    <mergeCell ref="A143:A148"/>
+    <mergeCell ref="B143:B148"/>
+    <mergeCell ref="C143:C148"/>
+    <mergeCell ref="A150:F159"/>
+    <mergeCell ref="A161:F164"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1764,7 +3829,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23"/>
@@ -1815,7 +3880,7 @@
         </is>
       </c>
       <c r="B2" s="10">
-        <v>2771749</v>
+        <v>2872361</v>
       </c>
       <c r="C2" s="10">
         <v>0</v>
@@ -1826,10 +3891,10 @@
         </is>
       </c>
       <c r="E2" s="23">
-        <v>32338</v>
+        <v>32378</v>
       </c>
       <c r="F2" s="23">
-        <v>45324</v>
+        <v>45322</v>
       </c>
       <c r="G2" s="23">
         <v>46205</v>
@@ -1838,293 +3903,850 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>DETERMINED_DATE</t>
+          <t>NOC_DATE</t>
         </is>
       </c>
       <c r="B3" s="10">
-        <v>2025497</v>
+        <v>17630</v>
       </c>
       <c r="C3" s="10">
-        <v>26.9</v>
-      </c>
-      <c r="D3" s="24" t="inlineStr">
-        <is>
-          <t>0001-01-01</t>
-        </is>
+        <v>99.4</v>
+      </c>
+      <c r="D3" s="23">
+        <v>33175</v>
       </c>
       <c r="E3" s="23">
-        <v>32402</v>
+        <v>43579</v>
       </c>
       <c r="F3" s="23">
-        <v>45313</v>
+        <v>46057</v>
       </c>
       <c r="G3" s="23">
-        <v>46203</v>
+        <v>46205</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>ACTUAL_RTC_DATE</t>
+          <t>EVAL_LAST_CHANGE</t>
         </is>
       </c>
       <c r="B4" s="10">
-        <v>1969800</v>
+        <v>2872361</v>
       </c>
       <c r="C4" s="10">
-        <v>28.9</v>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>0702-03-01</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="D4" s="23">
+        <v>36768</v>
       </c>
       <c r="E4" s="23">
-        <v>33098</v>
+        <v>36768</v>
       </c>
       <c r="F4" s="23">
-        <v>45383</v>
+        <v>46168</v>
       </c>
       <c r="G4" s="23">
-        <v>46205</v>
+        <v>46207</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>ENF_ACTION_DATE</t>
+          <t>DATE_OF_REQUEST</t>
         </is>
       </c>
       <c r="B5" s="10">
-        <v>1838577</v>
+        <v>5795</v>
       </c>
       <c r="C5" s="10">
-        <v>33.7</v>
+        <v>99.8</v>
       </c>
       <c r="D5" s="23">
-        <v>28854</v>
+        <v>33094</v>
       </c>
       <c r="E5" s="23">
-        <v>32778</v>
+        <v>35444</v>
       </c>
       <c r="F5" s="23">
-        <v>45404</v>
+        <v>45384</v>
       </c>
       <c r="G5" s="23">
-        <v>46205</v>
+        <v>46063</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>EVAL_LAST_CHANGE</t>
+          <t>DATE_RESPONSE_RECEIVED</t>
         </is>
       </c>
       <c r="B6" s="10">
-        <v>2771749</v>
+        <v>2945</v>
       </c>
       <c r="C6" s="10">
-        <v>0</v>
+        <v>99.9</v>
       </c>
       <c r="D6" s="23">
-        <v>36768</v>
+        <v>33554</v>
       </c>
       <c r="E6" s="23">
-        <v>36768</v>
+        <v>35419</v>
       </c>
       <c r="F6" s="23">
-        <v>46168</v>
+        <v>45250</v>
       </c>
       <c r="G6" s="23">
-        <v>46207</v>
+        <v>45897</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PROPOSED_AMOUNT</t>
+          <t>DETERMINED_DATE</t>
         </is>
       </c>
       <c r="B7" s="10">
-        <v>109874</v>
+        <v>2126109</v>
       </c>
       <c r="C7" s="10">
-        <v>96</v>
-      </c>
-      <c r="D7" s="10">
-        <v>0</v>
-      </c>
-      <c r="E7" s="10">
-        <v>1500</v>
-      </c>
-      <c r="F7" s="10">
-        <v>1330872.5</v>
-      </c>
-      <c r="G7" s="10">
-        <v>72290000</v>
+        <v>26</v>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>0001-01-01</t>
+        </is>
+      </c>
+      <c r="E7" s="23">
+        <v>32454</v>
+      </c>
+      <c r="F7" s="23">
+        <v>45301</v>
+      </c>
+      <c r="G7" s="23">
+        <v>46203</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>FINAL_MONETARY_AMOUNT</t>
+          <t>SCHEDULED_COMPLIANCE_DATE</t>
         </is>
       </c>
       <c r="B8" s="10">
-        <v>238842</v>
+        <v>535309</v>
       </c>
       <c r="C8" s="10">
-        <v>91.4</v>
-      </c>
-      <c r="D8" s="10">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10">
-        <v>1100</v>
-      </c>
-      <c r="F8" s="10">
-        <v>231000</v>
-      </c>
-      <c r="G8" s="10">
-        <v>122226400</v>
+        <v>81.4</v>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>0117-10-10</t>
+        </is>
+      </c>
+      <c r="E8" s="23">
+        <v>31982</v>
+      </c>
+      <c r="F8" s="23">
+        <v>43940</v>
+      </c>
+      <c r="G8" s="23">
+        <v>2958216</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PAID_AMOUNT</t>
+          <t>ACTUAL_RTC_DATE</t>
         </is>
       </c>
       <c r="B9" s="10">
-        <v>170827</v>
+        <v>2066477</v>
       </c>
       <c r="C9" s="10">
-        <v>93.8</v>
-      </c>
-      <c r="D9" s="10">
-        <v>0</v>
-      </c>
-      <c r="E9" s="10">
-        <v>1066</v>
-      </c>
-      <c r="F9" s="10">
-        <v>153697</v>
-      </c>
-      <c r="G9" s="10">
-        <v>12208769</v>
+        <v>28.1</v>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>0702-03-01</t>
+        </is>
+      </c>
+      <c r="E9" s="23">
+        <v>33156</v>
+      </c>
+      <c r="F9" s="23">
+        <v>45377</v>
+      </c>
+      <c r="G9" s="23">
+        <v>46205</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
+          <t>VIOL_LAST_CHANGE</t>
+        </is>
+      </c>
+      <c r="B10" s="10">
+        <v>2126107</v>
+      </c>
+      <c r="C10" s="10">
+        <v>26</v>
+      </c>
+      <c r="D10" s="23">
+        <v>36768</v>
+      </c>
+      <c r="E10" s="23">
+        <v>36768</v>
+      </c>
+      <c r="F10" s="23">
+        <v>46168</v>
+      </c>
+      <c r="G10" s="23">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>ENF_ACTION_DATE</t>
+        </is>
+      </c>
+      <c r="B11" s="10">
+        <v>1928016</v>
+      </c>
+      <c r="C11" s="10">
+        <v>32.9</v>
+      </c>
+      <c r="D11" s="23">
+        <v>28854</v>
+      </c>
+      <c r="E11" s="23">
+        <v>32842</v>
+      </c>
+      <c r="F11" s="23">
+        <v>45401</v>
+      </c>
+      <c r="G11" s="23">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>APPEAL_INITIATED_DATE</t>
+        </is>
+      </c>
+      <c r="B12" s="10">
+        <v>2515</v>
+      </c>
+      <c r="C12" s="10">
+        <v>99.9</v>
+      </c>
+      <c r="D12" s="23">
+        <v>37049</v>
+      </c>
+      <c r="E12" s="23">
+        <v>38804</v>
+      </c>
+      <c r="F12" s="23">
+        <v>45322</v>
+      </c>
+      <c r="G12" s="23">
+        <v>45917</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>APPEAL_RESOLVED_DATE</t>
+        </is>
+      </c>
+      <c r="B13" s="10">
+        <v>1040</v>
+      </c>
+      <c r="C13" s="10">
+        <v>100</v>
+      </c>
+      <c r="D13" s="23">
+        <v>37350</v>
+      </c>
+      <c r="E13" s="23">
+        <v>38817</v>
+      </c>
+      <c r="F13" s="23">
+        <v>42685</v>
+      </c>
+      <c r="G13" s="23">
+        <v>46049</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>DISPOSITION_STATUS_DATE</t>
+        </is>
+      </c>
+      <c r="B14" s="10">
+        <v>141287</v>
+      </c>
+      <c r="C14" s="10">
+        <v>95.1</v>
+      </c>
+      <c r="D14" s="23">
+        <v>30386</v>
+      </c>
+      <c r="E14" s="23">
+        <v>38575</v>
+      </c>
+      <c r="F14" s="23">
+        <v>45712</v>
+      </c>
+      <c r="G14" s="23">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>ENF_LAST_CHANGE</t>
+        </is>
+      </c>
+      <c r="B15" s="10">
+        <v>1978623</v>
+      </c>
+      <c r="C15" s="10">
+        <v>31.1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>36768</v>
+      </c>
+      <c r="E15" s="23">
+        <v>36768</v>
+      </c>
+      <c r="F15" s="23">
+        <v>45904</v>
+      </c>
+      <c r="G15" s="23">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>SCHEDULED_COMPLETION_DATE</t>
+        </is>
+      </c>
+      <c r="B16" s="10">
+        <v>27339</v>
+      </c>
+      <c r="C16" s="10">
+        <v>99</v>
+      </c>
+      <c r="D16" s="23">
+        <v>32405</v>
+      </c>
+      <c r="E16" s="23">
+        <v>35249</v>
+      </c>
+      <c r="F16" s="23">
+        <v>44166</v>
+      </c>
+      <c r="G16" s="23">
+        <v>46788</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>ACTUAL_COMPLETION_DATE</t>
+        </is>
+      </c>
+      <c r="B17" s="10">
+        <v>21646</v>
+      </c>
+      <c r="C17" s="10">
+        <v>99.2</v>
+      </c>
+      <c r="D17" s="23">
+        <v>32405</v>
+      </c>
+      <c r="E17" s="23">
+        <v>35202</v>
+      </c>
+      <c r="F17" s="23">
+        <v>43643</v>
+      </c>
+      <c r="G17" s="23">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>SEP_DEFAULTED_DATE</t>
+        </is>
+      </c>
+      <c r="B18" s="10">
+        <v>42</v>
+      </c>
+      <c r="C18" s="10">
+        <v>100</v>
+      </c>
+      <c r="D18" s="23">
+        <v>39454</v>
+      </c>
+      <c r="E18" s="23">
+        <v>39454</v>
+      </c>
+      <c r="F18" s="23">
+        <v>45560</v>
+      </c>
+      <c r="G18" s="23">
+        <v>45560</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>VIOL_SEQ</t>
+        </is>
+      </c>
+      <c r="B19" s="10">
+        <v>2126109</v>
+      </c>
+      <c r="C19" s="10">
+        <v>26</v>
+      </c>
+      <c r="D19" s="10">
+        <v>1</v>
+      </c>
+      <c r="E19" s="10">
+        <v>1</v>
+      </c>
+      <c r="F19" s="10">
+        <v>227</v>
+      </c>
+      <c r="G19" s="10">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>REQUEST_SEQ</t>
+        </is>
+      </c>
+      <c r="B20" s="10">
+        <v>5795</v>
+      </c>
+      <c r="C20" s="10">
+        <v>99.8</v>
+      </c>
+      <c r="D20" s="10">
+        <v>1</v>
+      </c>
+      <c r="E20" s="10">
+        <v>1</v>
+      </c>
+      <c r="F20" s="10">
+        <v>4</v>
+      </c>
+      <c r="G20" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>CITATION_SEQ</t>
+        </is>
+      </c>
+      <c r="B21" s="10">
+        <v>960878</v>
+      </c>
+      <c r="C21" s="10">
+        <v>66.5</v>
+      </c>
+      <c r="D21" s="10">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10">
+        <v>1</v>
+      </c>
+      <c r="F21" s="10">
+        <v>37252</v>
+      </c>
+      <c r="G21" s="10">
+        <v>56950</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>CAFO_SEQ</t>
+        </is>
+      </c>
+      <c r="B22" s="10">
+        <v>9186</v>
+      </c>
+      <c r="C22" s="10">
+        <v>99.7</v>
+      </c>
+      <c r="D22" s="10">
+        <v>3</v>
+      </c>
+      <c r="E22" s="10">
+        <v>25</v>
+      </c>
+      <c r="F22" s="10">
+        <v>70</v>
+      </c>
+      <c r="G22" s="10">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>SEP_SEQ</t>
+        </is>
+      </c>
+      <c r="B23" s="10">
+        <v>33116</v>
+      </c>
+      <c r="C23" s="10">
+        <v>98.8</v>
+      </c>
+      <c r="D23" s="10">
+        <v>1</v>
+      </c>
+      <c r="E23" s="10">
+        <v>1</v>
+      </c>
+      <c r="F23" s="10">
+        <v>5</v>
+      </c>
+      <c r="G23" s="10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>PROPOSED_AMOUNT</t>
+        </is>
+      </c>
+      <c r="B24" s="10">
+        <v>116430</v>
+      </c>
+      <c r="C24" s="10">
+        <v>95.9</v>
+      </c>
+      <c r="D24" s="10">
+        <v>0</v>
+      </c>
+      <c r="E24" s="10">
+        <v>1600</v>
+      </c>
+      <c r="F24" s="10">
+        <v>1328518</v>
+      </c>
+      <c r="G24" s="10">
+        <v>72290000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>FINAL_MONETARY_AMOUNT</t>
+        </is>
+      </c>
+      <c r="B25" s="10">
+        <v>257252</v>
+      </c>
+      <c r="C25" s="10">
+        <v>91</v>
+      </c>
+      <c r="D25" s="10">
+        <v>0</v>
+      </c>
+      <c r="E25" s="10">
+        <v>1170</v>
+      </c>
+      <c r="F25" s="10">
+        <v>225000</v>
+      </c>
+      <c r="G25" s="10">
+        <v>122226400</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>PAID_AMOUNT</t>
+        </is>
+      </c>
+      <c r="B26" s="10">
+        <v>185769</v>
+      </c>
+      <c r="C26" s="10">
+        <v>93.5</v>
+      </c>
+      <c r="D26" s="10">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10">
+        <v>1100</v>
+      </c>
+      <c r="F26" s="10">
+        <v>153697</v>
+      </c>
+      <c r="G26" s="10">
+        <v>12208769</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>FINAL_COUNT</t>
+        </is>
+      </c>
+      <c r="B27" s="10">
+        <v>257252</v>
+      </c>
+      <c r="C27" s="10">
+        <v>91</v>
+      </c>
+      <c r="D27" s="10">
+        <v>1</v>
+      </c>
+      <c r="E27" s="10">
+        <v>1</v>
+      </c>
+      <c r="F27" s="10">
+        <v>1</v>
+      </c>
+      <c r="G27" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
           <t>FINAL_AMOUNT</t>
         </is>
       </c>
-      <c r="B10" s="10">
-        <v>240810</v>
-      </c>
-      <c r="C10" s="10">
-        <v>91.3</v>
-      </c>
-      <c r="D10" s="10">
+      <c r="B28" s="10">
+        <v>259280</v>
+      </c>
+      <c r="C28" s="10">
+        <v>91</v>
+      </c>
+      <c r="D28" s="10">
         <v>0</v>
       </c>
-      <c r="E10" s="10">
-        <v>1250</v>
-      </c>
-      <c r="F10" s="10">
+      <c r="E28" s="10">
+        <v>1350</v>
+      </c>
+      <c r="F28" s="10">
         <v>250000</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G28" s="10">
         <v>123178777</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>EXPENDITURE_AMOUNT</t>
+        </is>
+      </c>
+      <c r="B29" s="10">
+        <v>24155</v>
+      </c>
+      <c r="C29" s="10">
+        <v>99.2</v>
+      </c>
+      <c r="D29" s="10">
+        <v>0</v>
+      </c>
+      <c r="E29" s="10">
+        <v>25</v>
+      </c>
+      <c r="F29" s="10">
+        <v>568311</v>
+      </c>
+      <c r="G29" s="10">
+        <v>40488024</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Notes on missing values:
+NOC_DATE: Not applicable. Only the evaluations that produced a notice of correction carry one.
+DATE_OF_REQUEST / DATE_RESPONSE_RECEIVED / REQUEST_SEQ: Not applicable. Few evaluations involve a formal information request.
 DETERMINED_DATE: Not applicable. These are the evaluations that didn't find a violation.
+SCHEDULED_COMPLIANCE_DATE: Not applicable. Set only where the agency scheduled a compliance date for the violation.
 ACTUAL_RTC_DATE: Missing. Either incomplete reporting or the agency hasn't designated RTC status yet.
 ENF_ACTION_DATE: Not applicable. These are the evaluations that didn't have an enforcement action followed.
+APPEAL_INITIATED_DATE / APPEAL_RESOLVED_DATE: Not applicable. Very few enforcement actions are appealed.
+DISPOSITION_STATUS_DATE: Not applicable. Recorded on the formal actions that reach a disposition.
 PROPOSED_AMOUNT: Not applicable. Not all enforcement actions have a proposed penalty, even the enforcement action has a penalty.
 FINAL_MONETARY_AMOUNT: Not applicable. Not all enforcement actions have a monetary penalty.
 PAID_AMOUNT: Not applicable or missing. Most likely because not all penalties are paid.
-FINAL_AMOUNT: Not applicable. N is larger than FINAL_MONETARY_AMOUNT because it reports the total penalties (final monetary penalty + Supplemental Environmental Project credit).</t>
-        </is>
-      </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
+FINAL_COUNT: Not applicable. It counts the final monetary order on the action, so it reads 1 wherever a final amount exists.
+FINAL_AMOUNT: Not applicable. N is larger than FINAL_MONETARY_AMOUNT because it reports the total penalties (final monetary penalty + Supplemental Environmental Project credit).
+SEP_SEQ / EXPENDITURE_AMOUNT / SCHEDULED_COMPLETION_DATE / ACTUAL_COMPLETION_DATE / SEP_DEFAULTED_DATE: Not applicable. Very few settlements include a supplemental environmental project, and fewer still default on one.
+CAFO_SEQ: Not applicable. Only the actions issued as a combined complaint and final order carry one.</t>
+        </is>
+      </c>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="14"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="14"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="14"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="14"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="14"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="14"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="14"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="14"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:G19"/>
+    <mergeCell ref="A31:G46"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2134,11 +4756,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="28.5"/>
-    <col min="2" max="7" bestFit="1" customWidth="1" hidden="false" width="12.664"/>
+    <col min="2" max="9" bestFit="1" customWidth="1" hidden="false" width="12.664"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2177,11 +4799,21 @@
           <t>No %</t>
         </is>
       </c>
+      <c r="H1" s="26" t="inlineStr">
+        <is>
+          <t>Unknown N</t>
+        </is>
+      </c>
+      <c r="I1" s="26" t="inlineStr">
+        <is>
+          <t>Unknown %</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>CITIZEN_COMPLAINT</t>
+          <t>FOUND_VIOLATION</t>
         </is>
       </c>
       <c r="B2" s="10">
@@ -2191,22 +4823,28 @@
         <v>0</v>
       </c>
       <c r="D2" s="10">
-        <v>117279</v>
+        <v>2125481</v>
       </c>
       <c r="E2" s="10">
-        <v>4.23</v>
+        <v>74</v>
       </c>
       <c r="F2" s="10">
-        <v>2654470</v>
+        <v>736758</v>
       </c>
       <c r="G2" s="10">
-        <v>95.77</v>
+        <v>25.65</v>
+      </c>
+      <c r="H2" s="10">
+        <v>10122</v>
+      </c>
+      <c r="I2" s="10">
+        <v>0.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>MULTIMEDIA_INSPECTION</t>
+          <t>CITIZEN_COMPLAINT</t>
         </is>
       </c>
       <c r="B3" s="10">
@@ -2216,22 +4854,28 @@
         <v>0</v>
       </c>
       <c r="D3" s="10">
-        <v>88081</v>
+        <v>122745</v>
       </c>
       <c r="E3" s="10">
-        <v>3.18</v>
+        <v>4.27</v>
       </c>
       <c r="F3" s="10">
-        <v>2683668</v>
+        <v>2749616</v>
       </c>
       <c r="G3" s="10">
-        <v>96.82</v>
+        <v>95.73</v>
+      </c>
+      <c r="H3" s="10">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>SAMPLING</t>
+          <t>MULTIMEDIA_INSPECTION</t>
         </is>
       </c>
       <c r="B4" s="10">
@@ -2241,22 +4885,28 @@
         <v>0</v>
       </c>
       <c r="D4" s="10">
-        <v>23214</v>
+        <v>92928</v>
       </c>
       <c r="E4" s="10">
-        <v>0.84</v>
+        <v>3.24</v>
       </c>
       <c r="F4" s="10">
-        <v>2748535</v>
+        <v>2779433</v>
       </c>
       <c r="G4" s="10">
-        <v>99.16</v>
+        <v>96.76</v>
+      </c>
+      <c r="H4" s="10">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>NOT_SUBTITLE_C</t>
+          <t>SAMPLING</t>
         </is>
       </c>
       <c r="B5" s="10">
@@ -2266,91 +4916,134 @@
         <v>0</v>
       </c>
       <c r="D5" s="10">
-        <v>2233</v>
+        <v>23648</v>
       </c>
       <c r="E5" s="10">
-        <v>0.08</v>
+        <v>0.82</v>
       </c>
       <c r="F5" s="10">
-        <v>2769516</v>
+        <v>2848713</v>
       </c>
       <c r="G5" s="10">
-        <v>99.92</v>
+        <v>99.18</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>CA_COMPONENT</t>
+          <t>NOT_SUBTITLE_C</t>
         </is>
       </c>
       <c r="B6" s="10">
-        <v>935737</v>
+        <v>0</v>
       </c>
       <c r="C6" s="10">
-        <v>33.76</v>
+        <v>0</v>
       </c>
       <c r="D6" s="10">
-        <v>29990</v>
+        <v>2249</v>
       </c>
       <c r="E6" s="10">
-        <v>1.08</v>
+        <v>0.08</v>
       </c>
       <c r="F6" s="10">
-        <v>1806022</v>
+        <v>2870112</v>
       </c>
       <c r="G6" s="10">
-        <v>65.16</v>
+        <v>99.92</v>
+      </c>
+      <c r="H6" s="10">
+        <v>0</v>
+      </c>
+      <c r="I6" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
+          <t>CA_COMPONENT</t>
+        </is>
+      </c>
+      <c r="B7" s="10">
+        <v>947167</v>
+      </c>
+      <c r="C7" s="10">
+        <v>32.98</v>
+      </c>
+      <c r="D7" s="10">
+        <v>31886</v>
+      </c>
+      <c r="E7" s="10">
+        <v>1.11</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1893308</v>
+      </c>
+      <c r="G7" s="10">
+        <v>65.91</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
           <t>FA_REQUIREMENT</t>
         </is>
       </c>
-      <c r="B7" s="10">
-        <v>1348899</v>
-      </c>
-      <c r="C7" s="10">
-        <v>48.67</v>
-      </c>
-      <c r="D7" s="10">
+      <c r="B8" s="10">
+        <v>1370190</v>
+      </c>
+      <c r="C8" s="10">
+        <v>47.7</v>
+      </c>
+      <c r="D8" s="10">
         <v>74</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E8" s="10">
         <v>0</v>
       </c>
-      <c r="F7" s="10">
-        <v>1422776</v>
-      </c>
-      <c r="G7" s="10">
-        <v>51.33</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="F8" s="10">
+        <v>1502097</v>
+      </c>
+      <c r="G8" s="10">
+        <v>52.29</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Notes on missing values:
+FOUND_VIOLATION: Unknown ('U') is EPA's own undetermined code.
 CA_COMPONENT: Missing. Incomplete reporting.
-FA_REQUIREMENT: Missing, but more likely N.</t>
-        </is>
-      </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="14"/>
+FA_REQUIREMENT: Missing, but more likely 0.</t>
+        </is>
+      </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
     </row>
     <row r="11">
       <c r="A11" s="14"/>
@@ -2360,10 +5053,34 @@
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:G11"/>
+    <mergeCell ref="A10:I13"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
